--- a/historical_vendor_database.xlsx
+++ b/historical_vendor_database.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Historical Vendor Database" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Historical Vendor Database" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E396"/>
+  <dimension ref="A1:E399"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -10318,6 +10318,81 @@
         </is>
       </c>
     </row>
+    <row r="397">
+      <c r="A397" t="inlineStr">
+        <is>
+          <t>LA BONNE SOUPE</t>
+        </is>
+      </c>
+      <c r="B397" t="inlineStr">
+        <is>
+          <t>80.21.11</t>
+        </is>
+      </c>
+      <c r="C397" t="inlineStr">
+        <is>
+          <t>G&amp;A Meals</t>
+        </is>
+      </c>
+      <c r="D397" t="n">
+        <v>1</v>
+      </c>
+      <c r="E397" t="inlineStr">
+        <is>
+          <t>Promoted from review</t>
+        </is>
+      </c>
+    </row>
+    <row r="398">
+      <c r="A398" t="inlineStr">
+        <is>
+          <t>LITTLE BEET (SEAMLESS)</t>
+        </is>
+      </c>
+      <c r="B398" t="inlineStr">
+        <is>
+          <t>80.21.11</t>
+        </is>
+      </c>
+      <c r="C398" t="inlineStr">
+        <is>
+          <t>G&amp;A Meals</t>
+        </is>
+      </c>
+      <c r="D398" t="n">
+        <v>1</v>
+      </c>
+      <c r="E398" t="inlineStr">
+        <is>
+          <t>Promoted from review</t>
+        </is>
+      </c>
+    </row>
+    <row r="399">
+      <c r="A399" t="inlineStr">
+        <is>
+          <t>IHG</t>
+        </is>
+      </c>
+      <c r="B399" t="inlineStr">
+        <is>
+          <t>80.21.05</t>
+        </is>
+      </c>
+      <c r="C399" t="inlineStr">
+        <is>
+          <t>G&amp;A Travel</t>
+        </is>
+      </c>
+      <c r="D399" t="n">
+        <v>1</v>
+      </c>
+      <c r="E399" t="inlineStr">
+        <is>
+          <t>Promoted from review</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/historical_vendor_database.xlsx
+++ b/historical_vendor_database.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E399"/>
+  <dimension ref="A1:E402"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -10393,6 +10393,81 @@
         </is>
       </c>
     </row>
+    <row r="400">
+      <c r="A400" t="inlineStr">
+        <is>
+          <t>HOTEL ALEX JOHNSON RRAPID CITY</t>
+        </is>
+      </c>
+      <c r="B400" t="inlineStr">
+        <is>
+          <t>80.21.05</t>
+        </is>
+      </c>
+      <c r="C400" t="inlineStr">
+        <is>
+          <t>G&amp;A Travel</t>
+        </is>
+      </c>
+      <c r="D400" t="n">
+        <v>1</v>
+      </c>
+      <c r="E400" t="inlineStr">
+        <is>
+          <t>Promoted from review</t>
+        </is>
+      </c>
+    </row>
+    <row r="401">
+      <c r="A401" t="inlineStr">
+        <is>
+          <t>ENTERPRISE RENT-A-CARAPID CITY</t>
+        </is>
+      </c>
+      <c r="B401" t="inlineStr">
+        <is>
+          <t>80.21.05</t>
+        </is>
+      </c>
+      <c r="C401" t="inlineStr">
+        <is>
+          <t>G&amp;A Travel</t>
+        </is>
+      </c>
+      <c r="D401" t="n">
+        <v>1</v>
+      </c>
+      <c r="E401" t="inlineStr">
+        <is>
+          <t>Promoted from review</t>
+        </is>
+      </c>
+    </row>
+    <row r="402">
+      <c r="A402" t="inlineStr">
+        <is>
+          <t>TST* LA PARISIENNE 0NEW YORK</t>
+        </is>
+      </c>
+      <c r="B402" t="inlineStr">
+        <is>
+          <t>80.21.11</t>
+        </is>
+      </c>
+      <c r="C402" t="inlineStr">
+        <is>
+          <t>G&amp;A Meals</t>
+        </is>
+      </c>
+      <c r="D402" t="n">
+        <v>1</v>
+      </c>
+      <c r="E402" t="inlineStr">
+        <is>
+          <t>Promoted from review</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
